--- a/data/validation_reports/WQ6_Complete_UP.xlsx
+++ b/data/validation_reports/WQ6_Complete_UP.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,41 +511,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amethi</t>
+          <t>Agra</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -554,10 +554,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amroha</t>
+          <t>Aligarh</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -614,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Auraiya</t>
+          <t>Ambedkar Nagar</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -641,16 +641,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -691,41 +691,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ayodhya</t>
+          <t>Amethi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azamgarh</t>
+          <t>Amroha</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -794,10 +794,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -811,11 +811,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Baghpat</t>
+          <t>Auraiya</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -836,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -871,11 +871,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bahraich</t>
+          <t>Ayodhya</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -931,17 +931,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ballia</t>
+          <t>Azamgarh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -956,16 +956,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -991,11 +991,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Balrampur</t>
+          <t>Baghpat</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1016,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1034,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1051,23 +1051,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Banda</t>
+          <t>Bahraich</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1088,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1111,41 +1111,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bara Banki</t>
+          <t>Ballia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bareilly</t>
+          <t>Balrampur</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1231,7 +1231,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Basti</t>
+          <t>Banda</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1291,38 +1291,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bhadohi</t>
+          <t>Bara Banki</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1351,7 +1351,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bijnor</t>
+          <t>Bareilly</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Budaun</t>
+          <t>Basti</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1471,26 +1471,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bulandshahr</t>
+          <t>Bhadohi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chandauli</t>
+          <t>Bijnor</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1574,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chitrakoot</t>
+          <t>Budaun</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deoria</t>
+          <t>Bulandshahr</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Etah</t>
+          <t>Chandauli</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1771,17 +1771,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Etawah</t>
+          <t>Chitrakoot</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1802,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1814,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Farrukhabad</t>
+          <t>Deoria</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1856,28 +1856,28 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -1891,41 +1891,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fatehpur</t>
+          <t>Etah</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1951,53 +1951,53 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Firozabad</t>
+          <t>Etawah</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>12</v>
-      </c>
       <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gautam Buddha Nagar</t>
+          <t>Farrukhabad</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2071,38 +2071,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ghaziabad</t>
+          <t>Fatehpur</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -2131,41 +2131,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ghazipur</t>
+          <t>Firozabad</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gonda</t>
+          <t>Gautam Buddha Nagar</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2251,7 +2251,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gorakhpur</t>
+          <t>Ghaziabad</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hamirpur</t>
+          <t>Ghazipur</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2330,22 +2330,22 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hapur</t>
+          <t>Gonda</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2431,17 +2431,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hardoi</t>
+          <t>Gorakhpur</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -2491,17 +2491,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hathras</t>
+          <t>Hamirpur</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalaun</t>
+          <t>Hapur</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2611,17 +2611,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jaunpur</t>
+          <t>Hardoi</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -2671,17 +2671,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Hathras</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2731,29 +2731,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kannauj</t>
+          <t>Jalaun</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2762,10 +2762,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2774,10 +2774,10 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -2791,41 +2791,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kanpur Dehat</t>
+          <t>Jaunpur</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -2851,38 +2851,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kanpur Nagar</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -2911,29 +2911,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kasganj</t>
+          <t>Kannauj</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2942,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2954,10 +2954,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -2971,41 +2971,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kaushambi</t>
+          <t>Kanpur Dehat</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3031,38 +3031,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kheri</t>
+          <t>Kanpur Nagar</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3074,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -3091,23 +3091,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kushinagar</t>
+          <t>Kasganj</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lalitpur</t>
+          <t>Kaushambi</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3211,17 +3211,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Kheri</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3271,23 +3271,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mahoba</t>
+          <t>Kushinagar</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mahrajganj</t>
+          <t>Lalitpur</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mainpuri</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3451,29 +3451,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mathura</t>
+          <t>Mahoba</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3482,10 +3482,10 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mau</t>
+          <t>Mahrajganj</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3571,7 +3571,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Mainpuri</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3602,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -3631,29 +3631,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mirzapur</t>
+          <t>Mathura</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3662,10 +3662,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3674,10 +3674,10 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Moradabad</t>
+          <t>Mau</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -3734,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Muzaffarnagar</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -3811,7 +3811,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pilibhit</t>
+          <t>Mirzapur</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -3871,41 +3871,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pratapgarh</t>
+          <t>Moradabad</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3914,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -3931,41 +3931,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Prayagraj</t>
+          <t>Muzaffarnagar</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>2</v>
@@ -3991,53 +3991,53 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rae Bareli</t>
+          <t>Pilibhit</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
         <v>5</v>
-      </c>
-      <c r="L60" t="n">
-        <v>3</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" t="n">
-        <v>4</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4051,41 +4051,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rampur</t>
+          <t>Pratapgarh</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -4094,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saharanpur</t>
+          <t>Prayagraj</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -4121,22 +4121,22 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P62" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4171,42 +4171,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sambhal</t>
+          <t>Rae Bareli</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
+        <v>7</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" t="n">
         <v>3</v>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
@@ -4214,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sant Kabir Nagar</t>
+          <t>Rampur</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -4241,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4291,17 +4291,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Shahjahanpur</t>
+          <t>Saharanpur</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -4351,7 +4351,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Shamli</t>
+          <t>Sambhal</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -4411,11 +4411,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Shrawasti</t>
+          <t>Sant Kabir Nagar</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -4454,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -4471,11 +4471,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Siddharthnagar</t>
+          <t>Shahjahanpur</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -4496,13 +4496,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sitapur</t>
+          <t>Shamli</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -4591,53 +4591,53 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sonbhadra</t>
+          <t>Shrawasti</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>32</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>10</v>
-      </c>
-      <c r="L70" t="n">
-        <v>9</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>2</v>
-      </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -4651,17 +4651,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sultanpur</t>
+          <t>Siddharthnagar</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -4676,16 +4676,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -4711,41 +4711,41 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Unnao</t>
+          <t>Sitapur</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4754,10 +4754,10 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -4771,58 +4771,238 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Sonbhadra</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>32</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>10</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sultanpur</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>26</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unnao</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>25</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Varanasi</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" t="n">
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
         <v>5</v>
       </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>4</v>
       </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
